--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="139">
   <si>
     <t>Materia</t>
   </si>
@@ -3380,13 +3380,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>41</v>
@@ -3396,93 +3396,105 @@
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="L2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -3503,7 +3515,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3524,7 +3536,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3535,13 +3547,22 @@
       <c r="S4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4">
+        <v>100</v>
+      </c>
+      <c r="V4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3562,7 +3583,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3583,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3594,13 +3615,22 @@
       <c r="S5">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:19">
+      <c r="T5">
+        <v>100</v>
+      </c>
+      <c r="U5">
+        <v>100</v>
+      </c>
+      <c r="V5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -3621,7 +3651,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3642,7 +3672,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3653,13 +3683,22 @@
       <c r="S6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6">
+        <v>100</v>
+      </c>
+      <c r="U6">
+        <v>100</v>
+      </c>
+      <c r="V6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3680,7 +3719,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3701,7 +3740,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3712,23 +3751,32 @@
       <c r="S7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7">
+        <v>100</v>
+      </c>
+      <c r="U7">
+        <v>100</v>
+      </c>
+      <c r="V7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
         <v>90</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>80</v>
       </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
       <c r="F8">
         <v>100</v>
       </c>
@@ -3739,17 +3787,17 @@
         <v>100</v>
       </c>
       <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
         <v>90</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>80</v>
       </c>
-      <c r="K8">
-        <v>100</v>
-      </c>
-      <c r="L8">
-        <v>100</v>
-      </c>
       <c r="M8">
         <v>100</v>
       </c>
@@ -3757,27 +3805,36 @@
         <v>100</v>
       </c>
       <c r="O8">
+        <v>100</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>100</v>
+      </c>
+      <c r="R8">
         <v>90</v>
       </c>
-      <c r="P8">
+      <c r="S8">
         <v>80</v>
       </c>
-      <c r="Q8">
-        <v>100</v>
-      </c>
-      <c r="R8">
-        <v>100</v>
-      </c>
-      <c r="S8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+      <c r="T8">
+        <v>100</v>
+      </c>
+      <c r="U8">
+        <v>100</v>
+      </c>
+      <c r="V8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -3798,7 +3855,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3819,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3830,13 +3887,22 @@
       <c r="S9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:19">
+      <c r="T9">
+        <v>100</v>
+      </c>
+      <c r="U9">
+        <v>100</v>
+      </c>
+      <c r="V9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -3857,7 +3923,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3878,7 +3944,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3889,22 +3955,31 @@
       <c r="S10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:19">
+      <c r="T10">
+        <v>100</v>
+      </c>
+      <c r="U10">
+        <v>100</v>
+      </c>
+      <c r="V10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>90</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3916,17 +3991,17 @@
         <v>100</v>
       </c>
       <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>100</v>
+      </c>
+      <c r="K11">
         <v>90</v>
       </c>
-      <c r="J11">
+      <c r="L11">
         <v>90</v>
       </c>
-      <c r="K11">
-        <v>100</v>
-      </c>
-      <c r="L11">
-        <v>100</v>
-      </c>
       <c r="M11">
         <v>100</v>
       </c>
@@ -3934,27 +4009,36 @@
         <v>100</v>
       </c>
       <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>100</v>
+      </c>
+      <c r="R11">
         <v>90</v>
       </c>
-      <c r="P11">
+      <c r="S11">
         <v>90</v>
       </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11">
+        <v>100</v>
+      </c>
+      <c r="U11">
+        <v>100</v>
+      </c>
+      <c r="V11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -3975,7 +4059,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -3996,7 +4080,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4007,23 +4091,32 @@
       <c r="S12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12">
+        <v>100</v>
+      </c>
+      <c r="U12">
+        <v>100</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
         <v>95</v>
       </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
       <c r="F13">
         <v>100</v>
       </c>
@@ -4034,17 +4127,17 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J13">
+        <v>100</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+      <c r="L13">
         <v>95</v>
       </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
       <c r="M13">
         <v>100</v>
       </c>
@@ -4055,34 +4148,43 @@
         <v>100</v>
       </c>
       <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>100</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
         <v>95</v>
       </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
-      <c r="R13">
-        <v>100</v>
-      </c>
-      <c r="S13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
+      <c r="T13">
+        <v>100</v>
+      </c>
+      <c r="U13">
+        <v>100</v>
+      </c>
+      <c r="V13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
         <v>70</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>80</v>
       </c>
-      <c r="E14">
-        <v>100</v>
-      </c>
       <c r="F14">
         <v>100</v>
       </c>
@@ -4093,17 +4195,17 @@
         <v>100</v>
       </c>
       <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>100</v>
+      </c>
+      <c r="K14">
         <v>70</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>80</v>
       </c>
-      <c r="K14">
-        <v>100</v>
-      </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
       <c r="M14">
         <v>100</v>
       </c>
@@ -4111,37 +4213,46 @@
         <v>100</v>
       </c>
       <c r="O14">
+        <v>100</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>100</v>
+      </c>
+      <c r="R14">
         <v>70</v>
       </c>
-      <c r="P14">
+      <c r="S14">
         <v>80</v>
       </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
-      <c r="R14">
-        <v>100</v>
-      </c>
-      <c r="S14">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+      <c r="T14">
+        <v>100</v>
+      </c>
+      <c r="U14">
+        <v>100</v>
+      </c>
+      <c r="V14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15">
         <v>95</v>
       </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
       <c r="F15">
         <v>100</v>
       </c>
@@ -4152,17 +4263,17 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15">
+        <v>100</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+      <c r="L15">
         <v>95</v>
       </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
       <c r="M15">
         <v>100</v>
       </c>
@@ -4173,34 +4284,40 @@
         <v>100</v>
       </c>
       <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>100</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
         <v>95</v>
       </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
-      <c r="R15">
-        <v>100</v>
-      </c>
-      <c r="S15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+      <c r="T15">
+        <v>100</v>
+      </c>
+      <c r="U15">
+        <v>100</v>
+      </c>
+      <c r="V15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16">
-        <v>100</v>
-      </c>
       <c r="C16">
+        <v>100</v>
+      </c>
+      <c r="D16">
         <v>90</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>80</v>
       </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
       <c r="F16">
         <v>100</v>
       </c>
@@ -4210,18 +4327,15 @@
       <c r="H16">
         <v>100</v>
       </c>
-      <c r="I16">
+      <c r="J16">
+        <v>100</v>
+      </c>
+      <c r="K16">
         <v>90</v>
       </c>
-      <c r="J16">
+      <c r="L16">
         <v>80</v>
       </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
       <c r="M16">
         <v>100</v>
       </c>
@@ -4229,37 +4343,43 @@
         <v>100</v>
       </c>
       <c r="O16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
+        <v>100</v>
+      </c>
+      <c r="R16">
         <v>90</v>
       </c>
-      <c r="P16">
+      <c r="S16">
         <v>80</v>
       </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
-      <c r="R16">
-        <v>100</v>
-      </c>
-      <c r="S16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="T16">
+        <v>100</v>
+      </c>
+      <c r="U16">
+        <v>100</v>
+      </c>
+      <c r="V16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
         <v>80</v>
       </c>
-      <c r="E17">
-        <v>100</v>
-      </c>
       <c r="F17">
         <v>100</v>
       </c>
@@ -4270,17 +4390,17 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J17">
+        <v>100</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
         <v>80</v>
       </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
       <c r="M17">
         <v>100</v>
       </c>
@@ -4291,34 +4411,43 @@
         <v>100</v>
       </c>
       <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>100</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
         <v>80</v>
       </c>
-      <c r="Q17">
-        <v>100</v>
-      </c>
-      <c r="R17">
-        <v>100</v>
-      </c>
-      <c r="S17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+      <c r="T17">
+        <v>100</v>
+      </c>
+      <c r="U17">
+        <v>100</v>
+      </c>
+      <c r="V17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C18">
+        <v>100</v>
+      </c>
+      <c r="D18">
         <v>80</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>75</v>
       </c>
-      <c r="E18">
-        <v>100</v>
-      </c>
       <c r="F18">
         <v>100</v>
       </c>
@@ -4329,17 +4458,17 @@
         <v>100</v>
       </c>
       <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>100</v>
+      </c>
+      <c r="K18">
         <v>80</v>
       </c>
-      <c r="J18">
+      <c r="L18">
         <v>75</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
         <v>100</v>
       </c>
@@ -4347,37 +4476,46 @@
         <v>100</v>
       </c>
       <c r="O18">
+        <v>100</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>100</v>
+      </c>
+      <c r="R18">
         <v>80</v>
       </c>
-      <c r="P18">
+      <c r="S18">
         <v>75</v>
       </c>
-      <c r="Q18">
-        <v>100</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>100</v>
+      </c>
+      <c r="V18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>100</v>
       </c>
       <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
         <v>85</v>
       </c>
-      <c r="E19">
-        <v>100</v>
-      </c>
       <c r="F19">
         <v>100</v>
       </c>
@@ -4388,17 +4526,17 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+      <c r="L19">
         <v>85</v>
       </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
       <c r="M19">
         <v>100</v>
       </c>
@@ -4409,24 +4547,33 @@
         <v>100</v>
       </c>
       <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>100</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>85</v>
       </c>
-      <c r="Q19">
-        <v>100</v>
-      </c>
-      <c r="R19">
-        <v>100</v>
-      </c>
-      <c r="S19">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
+      <c r="T19">
+        <v>100</v>
+      </c>
+      <c r="U19">
+        <v>100</v>
+      </c>
+      <c r="V19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -4447,7 +4594,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4468,7 +4615,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4479,13 +4626,22 @@
       <c r="S20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:19">
+      <c r="T20">
+        <v>100</v>
+      </c>
+      <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -4506,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4527,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4538,22 +4694,31 @@
       <c r="S21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:19">
+      <c r="T21">
+        <v>100</v>
+      </c>
+      <c r="U21">
+        <v>100</v>
+      </c>
+      <c r="V21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>90</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -4565,17 +4730,17 @@
         <v>100</v>
       </c>
       <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
         <v>90</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>90</v>
       </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
       <c r="M22">
         <v>100</v>
       </c>
@@ -4583,27 +4748,36 @@
         <v>100</v>
       </c>
       <c r="O22">
+        <v>100</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>100</v>
+      </c>
+      <c r="R22">
         <v>90</v>
       </c>
-      <c r="P22">
+      <c r="S22">
         <v>90</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
-        <v>100</v>
-      </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+      <c r="T22">
+        <v>100</v>
+      </c>
+      <c r="U22">
+        <v>100</v>
+      </c>
+      <c r="V22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -4624,7 +4798,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4645,7 +4819,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4656,20 +4830,29 @@
       <c r="S23">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:19">
+      <c r="T23">
+        <v>100</v>
+      </c>
+      <c r="U23">
+        <v>100</v>
+      </c>
+      <c r="V23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
         <v>90</v>
       </c>
-      <c r="D24">
-        <v>100</v>
-      </c>
       <c r="E24">
         <v>100</v>
       </c>
@@ -4683,14 +4866,14 @@
         <v>100</v>
       </c>
       <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>90</v>
       </c>
-      <c r="J24">
-        <v>100</v>
-      </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
       <c r="L24">
         <v>100</v>
       </c>
@@ -4701,34 +4884,43 @@
         <v>100</v>
       </c>
       <c r="O24">
+        <v>100</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>90</v>
       </c>
-      <c r="P24">
-        <v>100</v>
-      </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
       <c r="S24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:19">
+      <c r="T24">
+        <v>100</v>
+      </c>
+      <c r="U24">
+        <v>100</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
         <v>75</v>
       </c>
-      <c r="D25">
-        <v>100</v>
-      </c>
       <c r="E25">
         <v>100</v>
       </c>
@@ -4742,14 +4934,14 @@
         <v>100</v>
       </c>
       <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
         <v>75</v>
       </c>
-      <c r="J25">
-        <v>100</v>
-      </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
       <c r="L25">
         <v>100</v>
       </c>
@@ -4760,27 +4952,36 @@
         <v>100</v>
       </c>
       <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
         <v>75</v>
       </c>
-      <c r="P25">
-        <v>100</v>
-      </c>
-      <c r="Q25">
-        <v>100</v>
-      </c>
-      <c r="R25">
-        <v>100</v>
-      </c>
       <c r="S25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:19">
+      <c r="T25">
+        <v>100</v>
+      </c>
+      <c r="U25">
+        <v>100</v>
+      </c>
+      <c r="V25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -4801,7 +5002,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -4822,7 +5023,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -4833,13 +5034,22 @@
       <c r="S26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:19">
+      <c r="T26">
+        <v>100</v>
+      </c>
+      <c r="U26">
+        <v>100</v>
+      </c>
+      <c r="V26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -4860,7 +5070,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -4881,7 +5091,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -4892,20 +5102,29 @@
       <c r="S27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:19">
+      <c r="T27">
+        <v>100</v>
+      </c>
+      <c r="U27">
+        <v>100</v>
+      </c>
+      <c r="V27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C28">
+        <v>100</v>
+      </c>
+      <c r="D28">
         <v>85</v>
       </c>
-      <c r="D28">
-        <v>100</v>
-      </c>
       <c r="E28">
         <v>100</v>
       </c>
@@ -4919,14 +5138,14 @@
         <v>100</v>
       </c>
       <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>100</v>
+      </c>
+      <c r="K28">
         <v>85</v>
       </c>
-      <c r="J28">
-        <v>100</v>
-      </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
       <c r="L28">
         <v>100</v>
       </c>
@@ -4937,37 +5156,46 @@
         <v>100</v>
       </c>
       <c r="O28">
+        <v>100</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>100</v>
+      </c>
+      <c r="R28">
         <v>85</v>
       </c>
-      <c r="P28">
-        <v>100</v>
-      </c>
-      <c r="Q28">
-        <v>100</v>
-      </c>
-      <c r="R28">
-        <v>100</v>
-      </c>
       <c r="S28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:19">
+      <c r="T28">
+        <v>100</v>
+      </c>
+      <c r="U28">
+        <v>100</v>
+      </c>
+      <c r="V28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C29">
+        <v>100</v>
+      </c>
+      <c r="D29">
         <v>70</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>80</v>
       </c>
-      <c r="E29">
-        <v>100</v>
-      </c>
       <c r="F29">
         <v>100</v>
       </c>
@@ -4978,17 +5206,17 @@
         <v>100</v>
       </c>
       <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
         <v>70</v>
       </c>
-      <c r="J29">
+      <c r="L29">
         <v>80</v>
       </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
       <c r="M29">
         <v>100</v>
       </c>
@@ -4996,37 +5224,46 @@
         <v>100</v>
       </c>
       <c r="O29">
+        <v>100</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="R29">
         <v>70</v>
       </c>
-      <c r="P29">
+      <c r="S29">
         <v>80</v>
       </c>
-      <c r="Q29">
-        <v>100</v>
-      </c>
-      <c r="R29">
-        <v>100</v>
-      </c>
-      <c r="S29">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
+      <c r="T29">
+        <v>100</v>
+      </c>
+      <c r="U29">
+        <v>100</v>
+      </c>
+      <c r="V29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C30">
         <v>100</v>
       </c>
       <c r="D30">
+        <v>100</v>
+      </c>
+      <c r="E30">
         <v>75</v>
       </c>
-      <c r="E30">
-        <v>100</v>
-      </c>
       <c r="F30">
         <v>100</v>
       </c>
@@ -5037,17 +5274,17 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J30">
+        <v>100</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+      <c r="L30">
         <v>75</v>
       </c>
-      <c r="K30">
-        <v>100</v>
-      </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
       <c r="M30">
         <v>100</v>
       </c>
@@ -5058,32 +5295,38 @@
         <v>100</v>
       </c>
       <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>100</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
         <v>75</v>
       </c>
-      <c r="Q30">
-        <v>100</v>
-      </c>
-      <c r="R30">
-        <v>100</v>
-      </c>
-      <c r="S30">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19">
+      <c r="T30">
+        <v>100</v>
+      </c>
+      <c r="U30">
+        <v>100</v>
+      </c>
+      <c r="V30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C31">
-        <v>100</v>
-      </c>
-      <c r="E31">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>100</v>
-      </c>
-      <c r="I31">
+      <c r="D31">
+        <v>100</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="H31">
         <v>100</v>
       </c>
       <c r="K31">
@@ -5095,18 +5338,21 @@
       <c r="O31">
         <v>100</v>
       </c>
-      <c r="Q31">
-        <v>100</v>
-      </c>
-      <c r="S31">
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>100</v>
+      </c>
+      <c r="V31">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="H1:M1"/>
-    <mergeCell ref="N1:S1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -179,27 +179,27 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Cruz Alejo José Armando</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,229 +212,67 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CHULIN</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ELVIRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>NUBE</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIJANO</t>
-  </si>
-  <si>
     <t>RICO</t>
   </si>
   <si>
-    <t>ROSALIANO</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>NAVARRO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>CUICAHUA</t>
   </si>
   <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>PEDRO EVER</t>
-  </si>
-  <si>
-    <t>NEIL</t>
-  </si>
-  <si>
-    <t>ANGEL ALDAIR</t>
-  </si>
-  <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CESAR SAID</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>JULIO</t>
-  </si>
-  <si>
-    <t>CELSO ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>WENCESLAO</t>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
   </si>
   <si>
     <t>CLEMENTE</t>
   </si>
   <si>
-    <t>JOSE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ANGEL DANIEL</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
     <t>DIEGO HUMBERTO</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>SINAI ANTONIO</t>
-  </si>
-  <si>
     <t>ZURIEL ELIHU</t>
   </si>
   <si>
-    <t>JORGE MARIO</t>
-  </si>
-  <si>
-    <t>ARIEL CHARBEL</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>LUIS REY</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
     <t>DARINKA</t>
-  </si>
-  <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
   </si>
 </sst>
 </file>
@@ -940,7 +778,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>7</v>
@@ -961,25 +799,25 @@
         <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1003,7 +841,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -1012,7 +850,7 @@
         <v>8</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -1029,7 +867,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1050,25 +888,25 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1092,16 +930,16 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1118,7 +956,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -1139,25 +977,25 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1181,7 +1019,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1190,16 +1028,16 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1207,7 +1045,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -1228,25 +1066,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1270,7 +1108,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1279,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1296,7 +1134,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1317,25 +1155,25 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1359,16 +1197,16 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>10</v>
@@ -1385,7 +1223,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>8</v>
@@ -1406,25 +1244,25 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1448,16 +1286,16 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -1474,7 +1312,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>7</v>
@@ -1495,25 +1333,25 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1537,7 +1375,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1546,10 +1384,10 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1563,7 +1401,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1584,25 +1422,25 @@
         <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1626,19 +1464,19 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB11">
         <v>5</v>
@@ -1652,7 +1490,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>7</v>
@@ -1673,25 +1511,25 @@
         <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1715,19 +1553,19 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1741,7 +1579,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>7</v>
@@ -1762,25 +1600,25 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1804,25 +1642,25 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1830,7 +1668,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1851,25 +1689,25 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1893,16 +1731,16 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>9</v>
@@ -1911,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1919,7 +1757,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>7</v>
@@ -1940,25 +1778,25 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1982,19 +1820,19 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>10</v>
@@ -2026,22 +1864,22 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2062,16 +1900,16 @@
         <v>-1</v>
       </c>
       <c r="X16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB16">
         <v>6</v>
@@ -2085,7 +1923,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -2106,25 +1944,25 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2148,25 +1986,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2174,7 +2012,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2195,25 +2033,25 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2237,7 +2075,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -2249,7 +2087,7 @@
         <v>5</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -2263,7 +2101,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2284,25 +2122,25 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2326,7 +2164,7 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2335,16 +2173,16 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2352,7 +2190,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -2373,25 +2211,25 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2415,25 +2253,25 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2441,7 +2279,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2462,25 +2300,25 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2504,7 +2342,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2522,7 +2360,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2530,7 +2368,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -2551,25 +2389,25 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2593,7 +2431,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2602,10 +2440,10 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB22">
         <v>9</v>
@@ -2619,7 +2457,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>9</v>
@@ -2640,25 +2478,25 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2682,10 +2520,10 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2700,7 +2538,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2708,7 +2546,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2729,25 +2567,25 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2771,16 +2609,16 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -2797,7 +2635,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>7</v>
@@ -2818,25 +2656,25 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2860,25 +2698,25 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB25">
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2886,7 +2724,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>7</v>
@@ -2907,25 +2745,25 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2949,7 +2787,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>7</v>
@@ -2958,10 +2796,10 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB26">
         <v>10</v>
@@ -2975,7 +2813,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>7</v>
@@ -2996,25 +2834,25 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3038,7 +2876,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -3047,7 +2885,7 @@
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -3056,7 +2894,7 @@
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3064,7 +2902,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C28">
         <v>8</v>
@@ -3085,25 +2923,25 @@
         <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3127,7 +2965,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>8</v>
@@ -3136,10 +2974,10 @@
         <v>7</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>8</v>
@@ -3153,7 +2991,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -3174,25 +3012,25 @@
         <v>5</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3216,25 +3054,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29">
         <v>5</v>
       </c>
       <c r="AC29">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3242,7 +3080,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3263,25 +3101,25 @@
         <v>7</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3305,7 +3143,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3314,16 +3152,16 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AB30">
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3340,13 +3178,13 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3361,7 +3199,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3494,7 +3332,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4">
         <v>100</v>
@@ -3515,7 +3353,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -3524,7 +3362,7 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M4">
         <v>100</v>
@@ -3536,7 +3374,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -3545,7 +3383,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T4">
         <v>100</v>
@@ -3562,7 +3400,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>100</v>
@@ -3583,7 +3421,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>100</v>
@@ -3592,7 +3430,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -3604,7 +3442,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -3613,7 +3451,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -3630,7 +3468,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>100</v>
@@ -3651,7 +3489,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3660,7 +3498,7 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3672,7 +3510,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3681,7 +3519,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -3698,7 +3536,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -3719,7 +3557,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3728,7 +3566,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3740,7 +3578,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -3749,7 +3587,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -3766,7 +3604,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>100</v>
@@ -3787,19 +3625,19 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L8">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N8">
         <v>100</v>
@@ -3808,19 +3646,19 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S8">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -3834,7 +3672,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>100</v>
@@ -3855,7 +3693,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -3864,10 +3702,10 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -3876,7 +3714,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -3885,10 +3723,10 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U9">
         <v>100</v>
@@ -3902,7 +3740,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C10">
         <v>100</v>
@@ -3923,7 +3761,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3932,10 +3770,10 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3944,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3953,10 +3791,10 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -3970,7 +3808,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -3991,19 +3829,19 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -4012,19 +3850,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S11">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4038,7 +3876,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -4059,7 +3897,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -4068,7 +3906,7 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -4080,7 +3918,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4089,7 +3927,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T12">
         <v>100</v>
@@ -4106,7 +3944,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>100</v>
@@ -4127,7 +3965,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -4136,11 +3974,11 @@
         <v>100</v>
       </c>
       <c r="L13">
+        <v>97.5</v>
+      </c>
+      <c r="M13">
         <v>95</v>
       </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
       <c r="N13">
         <v>100</v>
       </c>
@@ -4148,7 +3986,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4157,10 +3995,10 @@
         <v>100</v>
       </c>
       <c r="S13">
+        <v>97.5</v>
+      </c>
+      <c r="T13">
         <v>95</v>
-      </c>
-      <c r="T13">
-        <v>100</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -4174,7 +4012,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -4195,19 +4033,19 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="L14">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -4216,19 +4054,19 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
         <v>100</v>
       </c>
       <c r="R14">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="S14">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="T14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U14">
         <v>100</v>
@@ -4242,7 +4080,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -4263,7 +4101,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>100</v>
@@ -4272,10 +4110,10 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -4284,7 +4122,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4293,10 +4131,10 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -4331,13 +4169,13 @@
         <v>100</v>
       </c>
       <c r="K16">
+        <v>70</v>
+      </c>
+      <c r="L16">
         <v>90</v>
       </c>
-      <c r="L16">
-        <v>80</v>
-      </c>
       <c r="M16">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N16">
         <v>100</v>
@@ -4349,13 +4187,13 @@
         <v>100</v>
       </c>
       <c r="R16">
+        <v>70</v>
+      </c>
+      <c r="S16">
         <v>90</v>
       </c>
-      <c r="S16">
-        <v>80</v>
-      </c>
       <c r="T16">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -4369,7 +4207,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -4390,7 +4228,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>100</v>
@@ -4399,10 +4237,10 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N17">
         <v>100</v>
@@ -4411,7 +4249,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -4420,10 +4258,10 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -4437,7 +4275,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -4458,46 +4296,46 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L18">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="N18">
         <v>100</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
         <v>100</v>
       </c>
       <c r="R18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S18">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="T18">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4505,7 +4343,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -4526,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -4535,10 +4373,10 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4547,7 +4385,7 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -4556,10 +4394,10 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -4573,7 +4411,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -4594,7 +4432,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>100</v>
@@ -4603,7 +4441,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -4615,7 +4453,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4624,7 +4462,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -4641,7 +4479,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -4662,7 +4500,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -4674,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -4683,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
         <v>100</v>
@@ -4695,7 +4533,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -4709,7 +4547,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -4730,19 +4568,19 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4751,19 +4589,19 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S22">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -4777,7 +4615,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -4798,7 +4636,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -4810,7 +4648,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4819,7 +4657,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -4831,7 +4669,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -4845,7 +4683,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -4866,19 +4704,19 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N24">
         <v>100</v>
@@ -4887,19 +4725,19 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
         <v>100</v>
       </c>
       <c r="R24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -4913,7 +4751,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -4934,19 +4772,19 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4955,19 +4793,19 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -4981,7 +4819,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5002,7 +4840,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>100</v>
@@ -5011,7 +4849,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -5023,7 +4861,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -5032,7 +4870,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -5049,7 +4887,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5070,7 +4908,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>100</v>
@@ -5079,7 +4917,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -5091,7 +4929,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -5100,7 +4938,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -5117,7 +4955,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5138,19 +4976,19 @@
         <v>100</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -5159,19 +4997,19 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
         <v>100</v>
       </c>
       <c r="R28">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -5185,7 +5023,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C29">
         <v>100</v>
@@ -5206,19 +5044,19 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L29">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -5227,19 +5065,19 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="S29">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U29">
         <v>100</v>
@@ -5253,7 +5091,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C30">
         <v>100</v>
@@ -5274,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5283,7 +5121,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -5295,7 +5133,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5304,7 +5142,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -5402,36 +5240,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="G2" s="2">
+        <v>25.9</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>26</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -5452,7 +5293,7 @@
         <v>25.9</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5495,28 +5336,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>88.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="G5" s="2">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5527,28 +5368,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>25</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>89.3</v>
+        <v>96.2</v>
       </c>
       <c r="G6" s="2">
-        <v>10.7</v>
+        <v>3.8</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5580,7 +5421,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5591,7 +5432,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -5612,7 +5453,7 @@
         <v>3.6</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5628,7 +5469,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5655,526 +5496,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920185</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920186</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920187</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920189</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920190</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920191</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920192</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>116</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330061430023</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920194</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920196</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920386</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920199</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920201</v>
-      </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920202</v>
-      </c>
-      <c r="B15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920203</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" t="s">
-        <v>124</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920204</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920205</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920206</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>104</v>
-      </c>
-      <c r="D19" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920207</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920208</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920209</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>130</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920210</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920211</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920212</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920213</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920214</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" t="s">
-        <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6182,7 +5503,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6217,22 +5538,22 @@
         <v>21330051920190</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -6240,16 +5561,16 @@
         <v>21330051920190</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -6260,39 +5581,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330061430023</v>
+        <v>21330051920213</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330061430023</v>
+        <v>21330051920213</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6306,42 +5627,42 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920205</v>
+        <v>20330051920100</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920205</v>
+        <v>21330051920201</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
@@ -6352,25 +5673,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920208</v>
+        <v>21330051920205</v>
       </c>
       <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" t="s">
         <v>82</v>
       </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>129</v>
-      </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -6378,19 +5699,19 @@
         <v>21330051920208</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6398,439 +5719,25 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920209</v>
+        <v>21330051920214</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920209</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>130</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920185</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920186</v>
-      </c>
-      <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920187</v>
-      </c>
-      <c r="B14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920189</v>
-      </c>
-      <c r="B15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920191</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920192</v>
-      </c>
-      <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" t="s">
-        <v>116</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>53</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920194</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920196</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>88</v>
-      </c>
-      <c r="D19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>53</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920199</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920100</v>
-      </c>
-      <c r="B21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920201</v>
-      </c>
-      <c r="B22" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920204</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920206</v>
-      </c>
-      <c r="B24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920207</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920210</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920211</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920212</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>NUBE</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>NUBE</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
@@ -236,12 +236,12 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
@@ -257,10 +257,10 @@
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
   </si>
   <si>
     <t>CLEMENTE</t>
@@ -814,7 +814,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>9</v>
@@ -992,7 +992,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>8</v>
@@ -1034,7 +1034,7 @@
         <v>10</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1081,7 +1081,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1170,7 +1170,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>9</v>
@@ -1212,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>9</v>
@@ -1259,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -1348,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>9</v>
@@ -1437,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>7</v>
@@ -1526,7 +1526,7 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>8</v>
@@ -1568,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -1615,7 +1615,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>8</v>
@@ -1704,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1793,7 +1793,7 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>8</v>
@@ -1876,7 +1876,7 @@
         <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>6</v>
@@ -1912,7 +1912,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -1959,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -2001,7 +2001,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>8</v>
@@ -2048,7 +2048,7 @@
         <v>4</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>5</v>
@@ -2137,7 +2137,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>10</v>
@@ -2226,7 +2226,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>9</v>
@@ -2268,7 +2268,7 @@
         <v>9</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>8</v>
@@ -2315,7 +2315,7 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>10</v>
@@ -2357,7 +2357,7 @@
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC21">
         <v>10</v>
@@ -2404,7 +2404,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>9</v>
@@ -2446,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2493,7 +2493,7 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2582,7 +2582,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>9</v>
@@ -2671,7 +2671,7 @@
         <v>7</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>7</v>
@@ -2713,7 +2713,7 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2760,7 +2760,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>9</v>
@@ -2849,7 +2849,7 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
         <v>10</v>
@@ -2938,7 +2938,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>7</v>
@@ -3027,7 +3027,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>8</v>
@@ -3116,7 +3116,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>9</v>
@@ -3368,7 +3368,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3389,7 +3389,7 @@
         <v>100</v>
       </c>
       <c r="U4">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3436,7 +3436,7 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3457,7 +3457,7 @@
         <v>100</v>
       </c>
       <c r="U5">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3572,7 +3572,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3593,7 +3593,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3640,7 +3640,7 @@
         <v>95</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3661,7 +3661,7 @@
         <v>95</v>
       </c>
       <c r="U8">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3708,7 +3708,7 @@
         <v>95</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -3729,7 +3729,7 @@
         <v>95</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3776,7 +3776,7 @@
         <v>97.5</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3797,7 +3797,7 @@
         <v>97.5</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3844,7 +3844,7 @@
         <v>92.5</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3865,7 +3865,7 @@
         <v>92.5</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -3912,7 +3912,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -3933,7 +3933,7 @@
         <v>100</v>
       </c>
       <c r="U12">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -3980,7 +3980,7 @@
         <v>95</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4001,7 +4001,7 @@
         <v>95</v>
       </c>
       <c r="U13">
-        <v>100</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4048,7 +4048,7 @@
         <v>90</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4069,7 +4069,7 @@
         <v>90</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4116,7 +4116,7 @@
         <v>90</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -4137,7 +4137,7 @@
         <v>90</v>
       </c>
       <c r="U15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4178,7 +4178,7 @@
         <v>70</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -4196,7 +4196,7 @@
         <v>70</v>
       </c>
       <c r="U16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4243,7 +4243,7 @@
         <v>95</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4264,7 +4264,7 @@
         <v>95</v>
       </c>
       <c r="U17">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4311,7 +4311,7 @@
         <v>70</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="O18">
         <v>90.90000000000001</v>
@@ -4332,7 +4332,7 @@
         <v>70</v>
       </c>
       <c r="U18">
-        <v>100</v>
+        <v>77.8</v>
       </c>
       <c r="V18">
         <v>90.90000000000001</v>
@@ -4379,7 +4379,7 @@
         <v>95</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4400,7 +4400,7 @@
         <v>95</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4447,7 +4447,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -4468,7 +4468,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4515,7 +4515,7 @@
         <v>95</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4536,7 +4536,7 @@
         <v>95</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4583,7 +4583,7 @@
         <v>95</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -4604,7 +4604,7 @@
         <v>95</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4651,7 +4651,7 @@
         <v>95</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4672,7 +4672,7 @@
         <v>95</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4719,7 +4719,7 @@
         <v>95</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4740,7 +4740,7 @@
         <v>95</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4787,7 +4787,7 @@
         <v>95</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4808,7 +4808,7 @@
         <v>95</v>
       </c>
       <c r="U25">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -4855,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4876,7 +4876,7 @@
         <v>100</v>
       </c>
       <c r="U26">
-        <v>100</v>
+        <v>82.2</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4991,7 +4991,7 @@
         <v>95</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -5012,7 +5012,7 @@
         <v>95</v>
       </c>
       <c r="U28">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5059,7 +5059,7 @@
         <v>95</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -5080,7 +5080,7 @@
         <v>95</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5127,7 +5127,7 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O30">
         <v>100</v>
@@ -5148,7 +5148,7 @@
         <v>100</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5313,19 +5313,19 @@
         <v>27</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="G4" s="2">
-        <v>18.5</v>
+        <v>22.2</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5503,7 +5503,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5581,7 +5581,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920213</v>
+        <v>20330051920100</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -5593,10 +5593,10 @@
         <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920213</v>
+        <v>20330051920100</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -5627,7 +5627,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920100</v>
+        <v>21330051920213</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -5639,10 +5639,10 @@
         <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5650,22 +5650,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920201</v>
+        <v>21330051920213</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920205</v>
+        <v>21330051920201</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5696,16 +5696,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920208</v>
+        <v>21330051920205</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
@@ -5719,16 +5719,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920214</v>
+        <v>21330051920208</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5737,6 +5737,29 @@
         <v>53</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920214</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Medina Tolentino Elio</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
@@ -212,67 +212,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>CUICAHUA</t>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
   </si>
   <si>
     <t>JORGE GUILLERMO</t>
   </si>
   <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
     <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DIEGO HUMBERTO</t>
-  </si>
-  <si>
-    <t>ZURIEL ELIHU</t>
-  </si>
-  <si>
-    <t>DARINKA</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1119,7 @@
         <v>6</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -1200,7 +1182,7 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1671,7 +1653,7 @@
         <v>6</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>7</v>
@@ -1734,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -2015,7 +1997,7 @@
         <v>5</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>5</v>
@@ -2104,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>8</v>
@@ -2282,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2345,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2549,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2612,7 +2594,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -3083,7 +3065,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -3146,7 +3128,7 @@
         <v>9</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -5240,7 +5222,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5261,7 +5243,7 @@
         <v>25.9</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5272,7 +5254,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
@@ -5281,19 +5263,19 @@
         <v>27</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>74.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="G3" s="2">
-        <v>25.9</v>
+        <v>22.2</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5304,28 +5286,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>77.8</v>
+        <v>89.3</v>
       </c>
       <c r="G4" s="2">
-        <v>22.2</v>
+        <v>10.7</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5336,28 +5318,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>25</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>89.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="G5" s="2">
-        <v>10.7</v>
+        <v>7.4</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5503,7 +5485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5535,19 +5517,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920190</v>
+        <v>21330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -5558,19 +5540,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920190</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -5587,16 +5569,16 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5610,16 +5592,16 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5633,16 +5615,16 @@
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5656,16 +5638,16 @@
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5673,22 +5655,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920201</v>
+        <v>21330051920190</v>
       </c>
       <c r="B8" t="s">
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5696,70 +5678,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920205</v>
+        <v>21330051920201</v>
       </c>
       <c r="B9" t="s">
         <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920208</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920214</v>
-      </c>
-      <c r="B11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -179,21 +179,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Elio</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>Garcia Felix Jose Antonio</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Elio</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
@@ -212,49 +212,49 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>LORENZO</t>
   </si>
   <si>
-    <t>NUBE</t>
+    <t>PEREZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
+    <t>ALEMAN</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>ALEMAN</t>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
   </si>
   <si>
     <t>GREGORIO</t>
   </si>
   <si>
-    <t>CHRISTIAN YAIR</t>
+    <t>ANGEL DANIEL</t>
   </si>
   <si>
     <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
   </si>
 </sst>
 </file>
@@ -802,31 +802,31 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>9</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -891,25 +891,25 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -918,7 +918,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5">
         <v>8</v>
@@ -980,25 +980,25 @@
         <v>8</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1010,10 +1010,10 @@
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>9</v>
@@ -1069,25 +1069,25 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1099,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1158,25 +1158,25 @@
         <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1188,10 +1188,10 @@
         <v>7</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>8</v>
@@ -1247,31 +1247,31 @@
         <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1336,28 +1336,28 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1425,43 +1425,43 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y11">
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -1514,40 +1514,40 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>10</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1603,28 +1603,28 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1692,25 +1692,25 @@
         <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1719,16 +1719,16 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1781,37 +1781,37 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y15">
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
@@ -1820,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1864,25 +1864,25 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -1894,7 +1894,7 @@
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>6</v>
@@ -1947,46 +1947,46 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>9</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
       </c>
       <c r="Z17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2036,25 +2036,25 @@
         <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>5</v>
@@ -2063,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2125,28 +2125,28 @@
         <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2155,13 +2155,13 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2214,25 +2214,25 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>10</v>
@@ -2253,7 +2253,7 @@
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2303,31 +2303,31 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>8</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2336,13 +2336,13 @@
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2392,25 +2392,25 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2422,13 +2422,13 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>8</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2481,31 +2481,31 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2570,25 +2570,25 @@
         <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2597,19 +2597,19 @@
         <v>7</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2659,25 +2659,25 @@
         <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>8</v>
@@ -2686,7 +2686,7 @@
         <v>7</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>7</v>
@@ -2695,7 +2695,7 @@
         <v>6</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>8</v>
@@ -2748,43 +2748,43 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>9</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
         <v>9</v>
@@ -2837,31 +2837,31 @@
         <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2926,31 +2926,31 @@
         <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2959,13 +2959,13 @@
         <v>9</v>
       </c>
       <c r="AA28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3015,25 +3015,25 @@
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3045,13 +3045,13 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC29">
         <v>7</v>
@@ -3104,28 +3104,28 @@
         <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>7</v>
@@ -3134,10 +3134,10 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3169,19 +3169,19 @@
         <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3365,13 +3365,13 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T4">
         <v>100</v>
       </c>
       <c r="U4">
-        <v>97.8</v>
+        <v>98.7</v>
       </c>
       <c r="V4">
         <v>100</v>
@@ -3433,13 +3433,13 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T5">
         <v>100</v>
       </c>
       <c r="U5">
-        <v>86.7</v>
+        <v>92</v>
       </c>
       <c r="V5">
         <v>100</v>
@@ -3501,10 +3501,10 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T6">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -3569,13 +3569,13 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T7">
         <v>100</v>
       </c>
       <c r="U7">
-        <v>91.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3634,16 +3634,16 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S8">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="T8">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U8">
-        <v>88.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -3705,13 +3705,13 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T9">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="U9">
-        <v>91.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3773,13 +3773,13 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T10">
-        <v>97.5</v>
+        <v>91.7</v>
       </c>
       <c r="U10">
-        <v>93.3</v>
+        <v>96</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3835,19 +3835,19 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S11">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="T11">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="U11">
-        <v>88.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="V11">
         <v>100</v>
@@ -3909,13 +3909,13 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="U12">
-        <v>91.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="V12">
         <v>100</v>
@@ -3977,13 +3977,13 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T13">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="U13">
-        <v>91.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="V13">
         <v>100</v>
@@ -4042,16 +4042,16 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>65</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S14">
-        <v>87.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="T14">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="U14">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="V14">
         <v>100</v>
@@ -4113,13 +4113,13 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>97.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="T15">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="U15">
-        <v>93.3</v>
+        <v>96</v>
       </c>
       <c r="V15">
         <v>100</v>
@@ -4169,16 +4169,16 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>70</v>
+        <v>81.3</v>
       </c>
       <c r="S16">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="T16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="U16">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="V16">
         <v>100</v>
@@ -4240,13 +4240,13 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="T17">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U17">
-        <v>84.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="V17">
         <v>100</v>
@@ -4305,19 +4305,19 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="S18">
-        <v>85</v>
+        <v>82.3</v>
       </c>
       <c r="T18">
-        <v>70</v>
+        <v>53.3</v>
       </c>
       <c r="U18">
-        <v>77.8</v>
+        <v>86.7</v>
       </c>
       <c r="V18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4376,13 +4376,13 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>90</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="T19">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U19">
-        <v>84.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -4444,13 +4444,13 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
       </c>
       <c r="U20">
-        <v>97.8</v>
+        <v>98.7</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -4515,10 +4515,10 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U21">
-        <v>88.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4577,16 +4577,16 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S22">
-        <v>92.5</v>
+        <v>93.5</v>
       </c>
       <c r="T22">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U22">
-        <v>86.7</v>
+        <v>92</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4651,10 +4651,10 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U23">
-        <v>97.8</v>
+        <v>98.7</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4713,16 +4713,16 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S24">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T24">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="U24">
-        <v>86.7</v>
+        <v>92</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4781,16 +4781,16 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="S25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T25">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="U25">
-        <v>82.2</v>
+        <v>89.3</v>
       </c>
       <c r="V25">
         <v>100</v>
@@ -4852,13 +4852,13 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="U26">
-        <v>82.2</v>
+        <v>89.3</v>
       </c>
       <c r="V26">
         <v>100</v>
@@ -4920,7 +4920,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -4985,16 +4985,16 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="T28">
         <v>95</v>
       </c>
       <c r="U28">
-        <v>97.8</v>
+        <v>98.7</v>
       </c>
       <c r="V28">
         <v>100</v>
@@ -5053,16 +5053,16 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S29">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="T29">
         <v>95</v>
       </c>
       <c r="U29">
-        <v>97.8</v>
+        <v>98.7</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -5124,13 +5124,13 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>87.5</v>
+        <v>90.3</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="U30">
-        <v>86.7</v>
+        <v>92</v>
       </c>
       <c r="V30">
         <v>100</v>
@@ -5162,7 +5162,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="V31">
         <v>100</v>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -5231,19 +5231,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>74.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="G2" s="2">
-        <v>25.9</v>
+        <v>14.8</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5254,25 +5254,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>54</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>77.8</v>
+        <v>89.3</v>
       </c>
       <c r="G3" s="2">
-        <v>22.2</v>
+        <v>10.7</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -5286,25 +5286,25 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>55</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4">
         <v>25</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>89.3</v>
+        <v>96.2</v>
       </c>
       <c r="G4" s="2">
-        <v>10.7</v>
+        <v>3.8</v>
       </c>
       <c r="H4">
         <v>8.5</v>
@@ -5318,7 +5318,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
@@ -5327,19 +5327,19 @@
         <v>27</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>92.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="G5" s="2">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5350,28 +5350,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6">
+        <v>27</v>
+      </c>
+      <c r="D6">
         <v>26</v>
-      </c>
-      <c r="D6">
-        <v>25</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="G6" s="2">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5403,7 +5403,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5423,19 +5423,19 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5485,7 +5485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920386</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -5529,7 +5529,7 @@
         <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>53</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920386</v>
+        <v>20330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -5552,7 +5552,7 @@
         <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
@@ -5563,7 +5563,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920100</v>
+        <v>19330061430023</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -5575,10 +5575,10 @@
         <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5586,22 +5586,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920100</v>
+        <v>21330051920386</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5609,19 +5609,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920213</v>
+        <v>21330051920203</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>53</v>
@@ -5635,67 +5635,21 @@
         <v>21330051920213</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>54</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920190</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920201</v>
-      </c>
-      <c r="B9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -823,16 +823,16 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -915,22 +915,22 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA5">
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1001,25 +1001,25 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1093,19 +1093,19 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA7">
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1179,25 +1179,25 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1271,22 +1271,22 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1357,25 +1357,25 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB10">
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1446,25 +1446,25 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1538,22 +1538,22 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1624,25 +1624,25 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1713,25 +1713,25 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1802,25 +1802,25 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB15">
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1885,19 +1885,19 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA16">
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1968,25 +1968,25 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2063,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2146,25 +2146,25 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2238,22 +2238,22 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2324,25 +2324,25 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z21">
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2413,25 +2413,25 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2502,13 +2502,13 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2591,25 +2591,25 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2680,25 +2680,25 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC25">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2769,25 +2769,25 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2858,16 +2858,16 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -2947,25 +2947,25 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3036,25 +3036,25 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA29">
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3125,25 +3125,25 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AB30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3178,10 +3178,10 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -5243,7 +5243,7 @@
         <v>14.8</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>10.7</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5307,7 +5307,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>3.7</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5403,7 +5403,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>0</v>

--- a/grupos/5BEM - Estadisticos 20231.xlsx
+++ b/grupos/5BEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="79">
   <si>
     <t>Materia</t>
   </si>
@@ -212,43 +212,43 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
     <t>NUBE</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ALEMAN</t>
   </si>
   <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
     <t>ROSALES</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
     <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
   </si>
   <si>
     <t>ANGEL DANIEL</t>
@@ -823,16 +823,16 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -915,22 +915,22 @@
         <v>10</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1001,25 +1001,25 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1093,19 +1093,19 @@
         <v>10</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
         <v>10</v>
@@ -1179,25 +1179,25 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1271,22 +1271,22 @@
         <v>10</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>10</v>
       </c>
       <c r="Z9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>10</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1357,25 +1357,25 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>10</v>
       </c>
       <c r="AC10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1446,25 +1446,25 @@
         <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1538,22 +1538,22 @@
         <v>10</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1624,25 +1624,25 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1713,25 +1713,25 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1802,25 +1802,25 @@
         <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB15">
         <v>10</v>
       </c>
       <c r="AC15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1864,7 +1864,7 @@
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>8</v>
@@ -1882,22 +1882,22 @@
         <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>5</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1968,25 +1968,25 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2063,7 +2063,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2075,7 +2075,7 @@
         <v>5</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2146,25 +2146,25 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2238,22 +2238,22 @@
         <v>10</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>10</v>
       </c>
       <c r="AC20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2324,25 +2324,25 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>10</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2413,25 +2413,25 @@
         <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2502,13 +2502,13 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <v>10</v>
@@ -2591,25 +2591,25 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC24">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2680,25 +2680,25 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2769,25 +2769,25 @@
         <v>9</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2858,16 +2858,16 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
       </c>
       <c r="Z27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA27">
         <v>10</v>
@@ -2947,25 +2947,25 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3036,25 +3036,25 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>5</v>
       </c>
       <c r="AB29">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC29">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3125,25 +3125,25 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3178,10 +3178,10 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -5231,19 +5231,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>85.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>14.8</v>
+        <v>11.1</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>10.7</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5307,7 +5307,7 @@
         <v>3.8</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>3.7</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5371,7 +5371,7 @@
         <v>3.7</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5403,7 +5403,7 @@
         <v>3.6</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5435,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -5485,7 +5485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5517,7 +5517,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920100</v>
+        <v>19330061430023</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -5540,22 +5540,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920100</v>
+        <v>21330051920386</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5563,22 +5563,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330061430023</v>
+        <v>20330051920100</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5586,22 +5586,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920386</v>
+        <v>21330051920203</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5609,47 +5609,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920203</v>
+        <v>21330051920213</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920213</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>
